--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Ferreteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72D2A1A-518C-4FF4-978E-60CA5B20CEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0790E895-23AA-4438-9DC6-77359CB89640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -386,7 +386,7 @@
     <t>Verificar lectura de Excel, SKU, stock, rack/columna/fila, búsqueda, idioma, interfaz móvil y logs en la URL desplegada; no declarar éxito sin probar.</t>
   </si>
   <si>
-    <t>Martillo de peña123</t>
+    <t>Martillo de peña1234567</t>
   </si>
 </sst>
 </file>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Ferreteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0790E895-23AA-4438-9DC6-77359CB89640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3861AF56-32B3-4F7E-8577-17074CD4E03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -386,7 +386,7 @@
     <t>Verificar lectura de Excel, SKU, stock, rack/columna/fila, búsqueda, idioma, interfaz móvil y logs en la URL desplegada; no declarar éxito sin probar.</t>
   </si>
   <si>
-    <t>Martillo de peña1234567</t>
+    <t>Martillo de peña123</t>
   </si>
 </sst>
 </file>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Ferreteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3861AF56-32B3-4F7E-8577-17074CD4E03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B12FCA-2180-41C8-8373-AC98699E603A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -386,7 +386,7 @@
     <t>Verificar lectura de Excel, SKU, stock, rack/columna/fila, búsqueda, idioma, interfaz móvil y logs en la URL desplegada; no declarar éxito sin probar.</t>
   </si>
   <si>
-    <t>Martillo de peña123</t>
+    <t>Martillo de peña12356</t>
   </si>
 </sst>
 </file>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Ferreteria\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B12FCA-2180-41C8-8373-AC98699E603A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="Inventario" sheetId="1" r:id="rId1"/>
-    <sheet name="Guia" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Inventario" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Guia" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -65,6 +59,9 @@
     <t>FER-001</t>
   </si>
   <si>
+    <t>Martillo de peña1235688</t>
+  </si>
+  <si>
     <t>Herramientas</t>
   </si>
   <si>
@@ -384,24 +381,28 @@
   </si>
   <si>
     <t>Verificar lectura de Excel, SKU, stock, rack/columna/fila, búsqueda, idioma, interfaz móvil y logs en la URL desplegada; no declarar éxito sin probar.</t>
-  </si>
-  <si>
-    <t>Martillo de peña12356</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -442,17 +443,17 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,21 +483,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaInventario" displayName="TablaInventario" ref="A1:M9" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="TablaInventario" displayName="TablaInventario" ref="A1:M9" totalsRowShown="1" headerRowCount="0">
+  <autoFilter>
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Producto"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Categoria"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Stock"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Rack"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Columna"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Fila"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Descripcion"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Marca"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Medida"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Unidad"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Sinonimos"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Especificaciones_tecnicas"/>
+    <tableColumn id="1" name="SKU"/>
+    <tableColumn id="2" name="Producto"/>
+    <tableColumn id="3" name="Categoria"/>
+    <tableColumn id="4" name="Stock"/>
+    <tableColumn id="5" name="Rack"/>
+    <tableColumn id="6" name="Columna"/>
+    <tableColumn id="7" name="Fila"/>
+    <tableColumn id="8" name="Descripcion"/>
+    <tableColumn id="9" name="Marca"/>
+    <tableColumn id="10" name="Medida"/>
+    <tableColumn id="11" name="Unidad"/>
+    <tableColumn id="12" name="Sinonimos"/>
+    <tableColumn id="13" name="Especificaciones_tecnicas"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -696,16 +712,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
@@ -714,367 +729,367 @@
     <col min="13" max="13" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32.1" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="32.1" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="36" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2">
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3">
+        <v>120</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="3">
+        <v>45</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D5" s="3">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="H7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="J7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="36" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="2">
-        <v>120</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="3">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="3">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="36" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="2">
-        <v>45</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="36" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2">
-        <v>6</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="H9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="36" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="2">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="36" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="2">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="36" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="2">
-        <v>11</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="J9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="K9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>78</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1083,8 +1098,11 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="whole" sqref="D2:D200" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="whole" sqref="D10:D200">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" sqref="D2:D200">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -1096,186 +1114,186 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="94" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B1" s="4"/>
+    </row>
+    <row r="2" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="3" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="4" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="5" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="6" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="7" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="8" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="9" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="10" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A11" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="2" t="s">
+    </row>
+    <row r="11" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="12" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.95" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="13" ht="30.95" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="15">
-      <c r="A14" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="15">
-      <c r="A15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15">
-      <c r="A16" s="4" t="s">
+    <row r="15" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B16" s="2" t="s">
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="29.25">
-      <c r="A17" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="2" t="s">
+    </row>
+    <row r="17" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="29.25">
-      <c r="A18" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="2" t="s">
+    </row>
+    <row r="18" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="29.25">
-      <c r="A19" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="2" t="s">
+    </row>
+    <row r="19" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="29.25">
-      <c r="A20" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B20" s="2" t="s">
+    </row>
+    <row r="20" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="29.25">
-      <c r="A21" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="2" t="s">
+    </row>
+    <row r="21" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="29.25">
-      <c r="A22" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="2" t="s">
+    </row>
+    <row r="22" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>120</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
